--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/9902-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/9902-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AE7BA7C-37C5-411E-BCC6-5A2905F780F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9994513-9F60-4692-9C9A-0CD12EE9A517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{9D8750E9-4405-4A71-A781-CEFD9D925C0A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D15CA01B-A2D2-460C-B5C5-3325E1CD815C}"/>
   </bookViews>
   <sheets>
     <sheet name="9902-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1484,28 +1484,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1872A924-C9C3-46A3-9372-11E9BF7C1CF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E14165-03F0-473D-B171-EBB3C23564D5}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1539,7 +1538,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1575,7 +1574,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1627,7 +1626,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1695,7 +1694,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1767,7 +1766,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1839,7 +1838,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1911,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -1983,7 +1982,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2055,7 +2054,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2127,7 +2126,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2199,7 +2198,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2271,7 +2270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2343,7 +2342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2415,7 +2414,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2487,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2559,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2631,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2703,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2775,7 +2774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2847,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2919,7 +2918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -2991,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2006</v>
       </c>
@@ -3063,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2005</v>
       </c>
@@ -3135,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2004</v>
       </c>
@@ -3207,7 +3206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2003</v>
       </c>
@@ -3279,7 +3278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2002</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2001</v>
       </c>
@@ -3423,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2000</v>
       </c>
@@ -3495,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>1999</v>
       </c>
@@ -3567,7 +3566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>1998</v>
       </c>
@@ -3639,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1997</v>
       </c>
@@ -3711,7 +3710,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>1996</v>
       </c>
@@ -3783,7 +3782,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1995</v>
       </c>
@@ -3855,7 +3854,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>1994</v>
       </c>
@@ -3927,7 +3926,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41"/>
       <c r="B36" s="42"/>
       <c r="C36" s="18" t="s">
@@ -3955,7 +3954,7 @@
       <c r="W36" s="48"/>
       <c r="X36" s="44"/>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1993</v>
       </c>
@@ -4027,7 +4026,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>1992</v>
       </c>
@@ -4099,7 +4098,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1991</v>
       </c>
@@ -4171,7 +4170,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>1990</v>
       </c>
@@ -4243,7 +4242,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1989</v>
       </c>
@@ -4315,7 +4314,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>1988</v>
       </c>
@@ -4387,7 +4386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>1987</v>
       </c>
@@ -4459,7 +4458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>1986</v>
       </c>
@@ -4531,7 +4530,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>1984</v>
       </c>
@@ -4603,7 +4602,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>1983</v>
       </c>
@@ -4675,7 +4674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37" t="s">
         <v>42</v>
       </c>
